--- a/disease_progression.xlsx
+++ b/disease_progression.xlsx
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.217</v>
+        <v>0.195</v>
       </c>
       <c r="D30">
-        <v>0.212</v>
+        <v>0.183</v>
       </c>
       <c r="E30">
-        <v>0.222</v>
+        <v>0.207</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.195</v>
+        <v>0.217</v>
       </c>
       <c r="D31">
-        <v>0.183</v>
+        <v>0.212</v>
       </c>
       <c r="E31">
-        <v>0.207</v>
+        <v>0.222</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="H36">
-        <v>32.45</v>
+        <v>21.45</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="J36">
-        <v>399.2</v>
+        <v>402.59</v>
       </c>
     </row>
     <row r="37">

--- a/disease_progression.xlsx
+++ b/disease_progression.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1980,17 +1980,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Duration of illness for severe chikungunya (years)</t>
+          <t>Duration of illness for mild and moderate Mayaro (years)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MAYV</t>
         </is>
       </c>
       <c r="C40">
-        <v>0.019</v>
+        <v>0.01917808219178083</v>
       </c>
       <c r="D40">
-        <v>0.008</v>
+        <v>0.01429457568193131</v>
       </c>
       <c r="E40">
-        <v>0.04</v>
+        <v>0.02572995832395412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2003,7 +2008,7 @@
         </is>
       </c>
       <c r="H40">
-        <v>-3.73</v>
+        <v>-3.953987204527178</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2011,24 +2016,24 @@
         </is>
       </c>
       <c r="J40">
-        <v>0.39</v>
+        <v>0.1499455777811528</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Duration of illness for sub-acute chikungunya (years)</t>
+          <t>Duration of illness for severe chikungunya (years)</t>
         </is>
       </c>
       <c r="C41">
-        <v>0.1</v>
+        <v>0.019</v>
       </c>
       <c r="D41">
+        <v>0.008</v>
+      </c>
+      <c r="E41">
         <v>0.04</v>
       </c>
-      <c r="E41">
-        <v>0.26</v>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>Lognormal</t>
@@ -2040,7 +2045,7 @@
         </is>
       </c>
       <c r="H41">
-        <v>-2.262311</v>
+        <v>-3.73</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2048,23 +2053,23 @@
         </is>
       </c>
       <c r="J41">
-        <v>0.4746817</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Duration of illness for chronic chikungunya (years)</t>
+          <t>Duration of illness for sub-acute chikungunya (years)</t>
         </is>
       </c>
       <c r="C42">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
       <c r="D42">
-        <v>0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E42">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
         </is>
       </c>
       <c r="H42">
-        <v>-0.6309</v>
+        <v>-2.262311</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2085,22 +2090,23 @@
         </is>
       </c>
       <c r="J42">
-        <v>0.0852</v>
+        <v>0.4746817</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Remaining life-years</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Age [0, 10)</t>
+          <t>Duration of illness for chronic chikungunya (years)</t>
         </is>
       </c>
       <c r="C43">
-        <v>70.90000000000001</v>
+        <v>0.53</v>
+      </c>
+      <c r="D43">
+        <v>0.46</v>
+      </c>
+      <c r="E43">
+        <v>0.64</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2113,7 +2119,7 @@
         </is>
       </c>
       <c r="H43">
-        <v>4.27</v>
+        <v>-0.6309</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2121,7 +2127,7 @@
         </is>
       </c>
       <c r="J43">
-        <v>0.05</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="44">
@@ -2132,11 +2138,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Age [10, 20)</t>
+          <t>Age [0, 10)</t>
         </is>
       </c>
       <c r="C44">
-        <v>61.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2149,7 +2155,7 @@
         </is>
       </c>
       <c r="H44">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2168,11 +2174,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Age [20, 30)</t>
+          <t>Age [10, 20)</t>
         </is>
       </c>
       <c r="C45">
-        <v>52.2</v>
+        <v>61.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2185,7 +2191,7 @@
         </is>
       </c>
       <c r="H45">
-        <v>3.96</v>
+        <v>4.12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2204,11 +2210,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Age [30, 40)</t>
+          <t>Age [20, 30)</t>
         </is>
       </c>
       <c r="C46">
-        <v>42.9</v>
+        <v>52.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2221,7 +2227,7 @@
         </is>
       </c>
       <c r="H46">
-        <v>3.76</v>
+        <v>3.96</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2240,11 +2246,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Age [40, 50)</t>
+          <t>Age [30, 40)</t>
         </is>
       </c>
       <c r="C47">
-        <v>33.9</v>
+        <v>42.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2257,7 +2263,7 @@
         </is>
       </c>
       <c r="H47">
-        <v>3.52</v>
+        <v>3.76</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2276,11 +2282,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Age [50, 60)</t>
+          <t>Age [40, 50)</t>
         </is>
       </c>
       <c r="C48">
-        <v>25.3</v>
+        <v>33.9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2293,7 +2299,7 @@
         </is>
       </c>
       <c r="H48">
-        <v>3.23</v>
+        <v>3.52</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2312,11 +2318,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Age [60, 70)</t>
+          <t>Age [50, 60)</t>
         </is>
       </c>
       <c r="C49">
-        <v>17.6</v>
+        <v>25.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2329,7 +2335,7 @@
         </is>
       </c>
       <c r="H49">
-        <v>2.87</v>
+        <v>3.23</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2348,11 +2354,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Age [70, 80)</t>
+          <t>Age [60, 70)</t>
         </is>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>17.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2365,7 +2371,7 @@
         </is>
       </c>
       <c r="H50">
-        <v>2.39</v>
+        <v>2.87</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2384,31 +2390,67 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>Age [70, 80)</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>11</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lognormal</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>meanlog</t>
+        </is>
+      </c>
+      <c r="H51">
+        <v>2.39</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>sdlog</t>
+        </is>
+      </c>
+      <c r="J51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Remaining life-years</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Age [80, 90)</t>
         </is>
       </c>
-      <c r="C51">
+      <c r="C52">
         <v>6.1</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Lognormal</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>meanlog</t>
         </is>
       </c>
-      <c r="H51">
+      <c r="H52">
         <v>1.81</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>sdlog</t>
         </is>
       </c>
-      <c r="J51">
+      <c r="J52">
         <v>0.05</v>
       </c>
     </row>
